--- a/SQExcel.Portal/src/content/docs/ja/docs/images/manual-entry/manual-entry.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/manual-entry/manual-entry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\manual-entry\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\manual-entry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A794F3-A0B1-4CBE-B67B-1D301302E996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D49F128-6264-414D-A830-6B6D72F44F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="17470" windowHeight="13490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="156" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MANUAL INPUT" sheetId="4" r:id="rId1"/>
@@ -231,22 +231,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>8964</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>8965</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>47</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>72316</xdr:rowOff>
+      <xdr:colOff>180414</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>65002</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D46227C-EA7B-B215-C791-6022036B90EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCA2F566-29FC-3FF8-0827-15E712B0836D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -262,8 +262,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="469900" y="1600200"/>
-          <a:ext cx="10801350" cy="5330116"/>
+          <a:off x="475129" y="1640541"/>
+          <a:ext cx="10660156" cy="5183849"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -539,12 +539,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16622AB1-2853-4282-ACE0-64F3E064F651}">
   <dimension ref="A2:B574"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -560,121 +560,121 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B31" s="2"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B38" s="2"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B43" s="2"/>
     </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B66" s="2"/>
     </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B68" s="2"/>
     </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B83" s="2"/>
     </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B93" s="2"/>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B107" s="2"/>
     </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B131" s="2"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B146" s="2"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B165" s="2"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B169" s="2"/>
     </row>
-    <row r="184" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B184" s="2"/>
     </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B204" s="2"/>
     </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B223" s="2"/>
     </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B237" s="2"/>
     </row>
-    <row r="250" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B250" s="2"/>
     </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B259" s="2"/>
     </row>
-    <row r="278" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B278" s="2"/>
     </row>
-    <row r="290" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B290" s="2"/>
     </row>
-    <row r="302" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B302" s="2"/>
     </row>
-    <row r="331" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B331" s="2"/>
     </row>
-    <row r="334" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B334" s="3"/>
     </row>
-    <row r="357" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B357" s="2"/>
     </row>
-    <row r="366" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B366" s="2"/>
     </row>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B384" s="2"/>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B385" s="2"/>
     </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B411" s="2"/>
     </row>
-    <row r="420" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B420" s="2"/>
     </row>
-    <row r="437" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="437" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B437" s="2"/>
     </row>
-    <row r="470" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="470" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B470" s="2"/>
     </row>
-    <row r="512" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="512" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B512" s="2"/>
     </row>
-    <row r="539" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="539" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B539" s="2"/>
     </row>
-    <row r="574" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="574" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B574" s="2"/>
     </row>
   </sheetData>
